--- a/docs/StructureDefinition-retina-ai-device.xlsx
+++ b/docs/StructureDefinition-retina-ai-device.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3112" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3112" uniqueCount="425">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,13 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-30T22:57:21+01:00</t>
+    <t>2025-12-02</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -1642,15 +1639,15 @@
         <v>35</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1705,121 +1702,121 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>73</v>
       </c>
-      <c r="AJ1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="AK1" t="s" s="1">
+      <c r="AL1" t="s" s="1">
         <v>75</v>
       </c>
-      <c r="AL1" t="s" s="1">
+      <c r="AM1" t="s" s="1">
         <v>76</v>
-      </c>
-      <c r="AM1" t="s" s="1">
-        <v>77</v>
       </c>
     </row>
     <row r="2">
@@ -1835,28 +1832,28 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="H2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="M2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1910,16 +1907,16 @@
         <v>32</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI2" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>32</v>
@@ -1933,10 +1930,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1944,31 +1941,31 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2018,13 +2015,13 @@
         <v>21</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>21</v>
@@ -2044,10 +2041,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2055,28 +2052,28 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2127,19 +2124,19 @@
         <v>21</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>21</v>
@@ -2153,10 +2150,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2164,31 +2161,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2238,19 +2235,19 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -2264,10 +2261,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2275,10 +2272,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2290,16 +2287,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2325,43 +2322,43 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
@@ -2375,21 +2372,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>21</v>
@@ -2401,16 +2398,16 @@
         <v>21</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2460,22 +2457,22 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>21</v>
@@ -2486,22 +2483,22 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
       </c>
@@ -2512,16 +2509,16 @@
         <v>21</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2571,22 +2568,22 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>21</v>
@@ -2597,22 +2594,22 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
       </c>
@@ -2623,16 +2620,16 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2682,22 +2679,22 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>136</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>21</v>
@@ -2708,10 +2705,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2719,28 +2716,28 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2791,19 +2788,19 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH10" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -2817,10 +2814,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2828,11 +2825,11 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G11" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G11" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2843,16 +2840,16 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2902,36 +2899,36 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH11" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2939,10 +2936,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -2954,13 +2951,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3011,19 +3008,19 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3037,10 +3034,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3048,11 +3045,11 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3060,19 +3057,19 @@
         <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3122,25 +3119,25 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -3148,10 +3145,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3159,10 +3156,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -3174,13 +3171,13 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3231,22 +3228,22 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
@@ -3257,22 +3254,22 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G15" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3283,16 +3280,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="M15" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3342,22 +3339,22 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH15" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
@@ -3368,45 +3365,45 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G16" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3455,22 +3452,22 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH16" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
@@ -3481,39 +3478,39 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3564,47 +3561,47 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>180</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3616,13 +3613,13 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3673,36 +3670,36 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3710,10 +3707,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3725,17 +3722,17 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3784,22 +3781,22 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
@@ -3810,42 +3807,42 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3895,68 +3892,68 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4006,36 +4003,36 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4043,10 +4040,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4058,17 +4055,17 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4093,46 +4090,46 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y22" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y22" t="s" s="2">
+      <c r="Z22" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Z22" t="s" s="2">
+      <c r="AA22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -4143,10 +4140,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4154,31 +4151,31 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4204,49 +4201,49 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AA23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK23" t="s" s="2">
+      <c r="AL23" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4254,10 +4251,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4265,11 +4262,11 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4280,13 +4277,13 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4313,14 +4310,14 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4337,25 +4334,25 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH24" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH24" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4363,21 +4360,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4389,16 +4386,16 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4448,36 +4445,36 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4485,10 +4482,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4500,13 +4497,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4557,36 +4554,36 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4594,10 +4591,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -4609,13 +4606,13 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4666,36 +4663,36 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4703,10 +4700,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -4718,13 +4715,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4775,36 +4772,36 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>249</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4812,10 +4809,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4827,13 +4824,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4884,36 +4881,36 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4921,10 +4918,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4936,16 +4933,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4995,25 +4992,25 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -5021,10 +5018,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5032,10 +5029,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5047,13 +5044,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5104,19 +5101,19 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH31" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH31" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
@@ -5130,10 +5127,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5141,10 +5138,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5156,13 +5153,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5213,22 +5210,22 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
@@ -5239,22 +5236,22 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G33" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G33" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5265,16 +5262,16 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5324,22 +5321,22 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH33" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH33" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
@@ -5350,10 +5347,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5361,28 +5358,28 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5433,19 +5430,19 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH34" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
@@ -5459,21 +5456,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -5485,13 +5482,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5542,19 +5539,19 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>21</v>
@@ -5568,10 +5565,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5579,10 +5576,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5594,13 +5591,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5612,64 +5609,64 @@
         <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y36" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="T36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y36" t="s" s="2">
+      <c r="Z36" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="Z36" t="s" s="2">
+      <c r="AA36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK36" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AA36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AL36" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -5677,10 +5674,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5688,10 +5685,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -5703,13 +5700,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5760,25 +5757,25 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -5786,10 +5783,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5797,10 +5794,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -5812,16 +5809,16 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="N38" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5871,25 +5868,25 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -5897,10 +5894,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5908,10 +5905,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -5923,13 +5920,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5956,14 +5953,14 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Z39" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
       </c>
@@ -5980,19 +5977,19 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
@@ -6006,10 +6003,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6017,11 +6014,11 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G40" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G40" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6032,13 +6029,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6089,19 +6086,19 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH40" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6115,10 +6112,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6126,10 +6123,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6141,13 +6138,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6198,22 +6195,22 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -6224,22 +6221,22 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6250,16 +6247,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L42" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="M42" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6309,22 +6306,22 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH42" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6335,45 +6332,45 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6422,22 +6419,22 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH43" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6448,21 +6445,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6474,13 +6471,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6531,19 +6528,19 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -6557,10 +6554,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6568,10 +6565,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6583,13 +6580,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6640,25 +6637,25 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6666,10 +6663,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6677,10 +6674,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6692,13 +6689,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6737,29 +6734,29 @@
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH46" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
@@ -6773,10 +6770,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6784,10 +6781,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -6799,13 +6796,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6856,22 +6853,22 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK47" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
@@ -6882,22 +6879,22 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G48" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
       </c>
@@ -6908,16 +6905,16 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="M48" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6967,22 +6964,22 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH48" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH48" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
@@ -6993,10 +6990,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7004,28 +7001,28 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7076,19 +7073,19 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH49" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH49" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -7102,21 +7099,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7128,13 +7125,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7185,19 +7182,19 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
@@ -7211,10 +7208,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7222,10 +7219,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7237,13 +7234,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7294,25 +7291,25 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7320,10 +7317,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7331,10 +7328,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7346,13 +7343,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7403,19 +7400,19 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -7429,23 +7426,23 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7457,13 +7454,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7514,19 +7511,19 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH53" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH53" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -7540,10 +7537,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7551,10 +7548,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7566,13 +7563,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7623,22 +7620,22 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK54" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
@@ -7649,22 +7646,22 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G55" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G55" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
       </c>
@@ -7675,16 +7672,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="M55" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7734,22 +7731,22 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH55" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH55" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
@@ -7760,10 +7757,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7771,28 +7768,28 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7843,19 +7840,19 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH56" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH56" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -7869,21 +7866,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -7895,13 +7892,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7913,7 +7910,7 @@
         <v>21</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>21</v>
@@ -7952,19 +7949,19 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -7978,10 +7975,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7989,10 +7986,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -8004,13 +8001,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8061,22 +8058,22 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK58" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
@@ -8087,10 +8084,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8098,10 +8095,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -8113,13 +8110,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8158,31 +8155,31 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AC59" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AC59" t="s" s="2">
-        <v>329</v>
-      </c>
       <c r="AD59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH59" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH59" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -8196,10 +8193,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8207,11 +8204,11 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G60" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G60" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8219,22 +8216,22 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8283,22 +8280,22 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK60" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
@@ -8309,10 +8306,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8320,10 +8317,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8332,22 +8329,22 @@
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8396,22 +8393,22 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
@@ -8422,10 +8419,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8433,10 +8430,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -8448,13 +8445,13 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8505,25 +8502,25 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
@@ -8531,10 +8528,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8542,10 +8539,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -8557,13 +8554,13 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8614,19 +8611,19 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -8640,23 +8637,23 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C64" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -8668,13 +8665,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8725,19 +8722,19 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH64" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH64" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
@@ -8751,10 +8748,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8762,10 +8759,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -8777,13 +8774,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8834,22 +8831,22 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK65" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
@@ -8860,22 +8857,22 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G66" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G66" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
       </c>
@@ -8886,16 +8883,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L66" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="M66" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8945,22 +8942,22 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH66" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH66" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
@@ -8971,10 +8968,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8982,28 +8979,28 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9054,19 +9051,19 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH67" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH67" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
@@ -9080,21 +9077,21 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -9106,13 +9103,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9124,7 +9121,7 @@
         <v>21</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>21</v>
@@ -9163,19 +9160,19 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
@@ -9189,10 +9186,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9200,10 +9197,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -9215,13 +9212,13 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9272,22 +9269,22 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK69" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>21</v>
@@ -9298,10 +9295,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9309,10 +9306,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -9324,13 +9321,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9369,31 +9366,31 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AC70" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AC70" t="s" s="2">
-        <v>329</v>
-      </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH70" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH70" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
@@ -9407,10 +9404,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9418,11 +9415,11 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G71" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G71" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9430,22 +9427,22 @@
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -9494,22 +9491,22 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK71" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
@@ -9520,10 +9517,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9531,10 +9528,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
@@ -9543,22 +9540,22 @@
         <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -9607,22 +9604,22 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK72" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
@@ -9633,10 +9630,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9644,10 +9641,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -9659,13 +9656,13 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9716,25 +9713,25 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
@@ -9742,10 +9739,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9753,10 +9750,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -9768,13 +9765,13 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9825,19 +9822,19 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
@@ -9851,10 +9848,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9862,11 +9859,11 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G75" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G75" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
       </c>
@@ -9877,13 +9874,13 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9934,19 +9931,19 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH75" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH75" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
@@ -9960,10 +9957,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9971,10 +9968,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -9986,13 +9983,13 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10043,22 +10040,22 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK76" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
@@ -10069,22 +10066,22 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G77" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G77" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10095,16 +10092,16 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L77" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="M77" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10154,22 +10151,22 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH77" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH77" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
@@ -10180,45 +10177,45 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G78" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G78" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10267,22 +10264,22 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH78" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH78" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>21</v>
@@ -10293,10 +10290,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10304,10 +10301,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>21</v>
@@ -10319,13 +10316,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10376,19 +10373,19 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
@@ -10402,10 +10399,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10413,11 +10410,11 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G80" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G80" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H80" t="s" s="2">
         <v>21</v>
       </c>
@@ -10428,13 +10425,13 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10485,19 +10482,19 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH80" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH80" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>21</v>
@@ -10511,10 +10508,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10522,11 +10519,11 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G81" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G81" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
       </c>
@@ -10537,13 +10534,13 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10594,19 +10591,19 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH81" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH81" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
@@ -10620,10 +10617,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10631,10 +10628,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
@@ -10646,17 +10643,17 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -10705,25 +10702,25 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>21</v>
@@ -10731,10 +10728,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10742,10 +10739,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -10757,13 +10754,13 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10814,25 +10811,25 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AL83" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
@@ -10840,10 +10837,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10851,11 +10848,11 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G84" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G84" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
       </c>
@@ -10866,16 +10863,16 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10925,25 +10922,25 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH84" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH84" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -10951,10 +10948,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10962,10 +10959,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>21</v>
@@ -10977,17 +10974,17 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -11036,25 +11033,25 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
@@ -11062,10 +11059,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11073,10 +11070,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>21</v>
@@ -11088,16 +11085,16 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11147,25 +11144,25 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
@@ -11173,10 +11170,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11184,11 +11181,11 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G87" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G87" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H87" t="s" s="2">
         <v>21</v>
       </c>
@@ -11199,13 +11196,13 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11256,22 +11253,22 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH87" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH87" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>21</v>
@@ -11282,10 +11279,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11293,11 +11290,11 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G88" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G88" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H88" t="s" s="2">
         <v>21</v>
       </c>
@@ -11305,16 +11302,16 @@
         <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11365,22 +11362,22 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH88" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AH88" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AI88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>21</v>
@@ -11391,10 +11388,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11402,10 +11399,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>21</v>
@@ -11417,13 +11414,13 @@
         <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11474,19 +11471,19 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>21</v>

--- a/docs/StructureDefinition-retina-ai-device.xlsx
+++ b/docs/StructureDefinition-retina-ai-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-ai-device.xlsx
+++ b/docs/StructureDefinition-retina-ai-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.8.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-ai-device.xlsx
+++ b/docs/StructureDefinition-retina-ai-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-ai-device.xlsx
+++ b/docs/StructureDefinition-retina-ai-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-ai-device.xlsx
+++ b/docs/StructureDefinition-retina-ai-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
